--- a/tests/v1/fixtures/office6m/2026-07/bank_statements/HB_B_USD_2026-06.xlsx
+++ b/tests/v1/fixtures/office6m/2026-07/bank_statements/HB_B_USD_2026-06.xlsx
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>704314.35</v>
+        <v>706464.35</v>
       </c>
       <c r="E2" t="n">
         <v>-30266.15</v>
       </c>
       <c r="F2" t="n">
-        <v>674048.2</v>
+        <v>676198.2</v>
       </c>
     </row>
     <row r="3">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>674048.2</v>
+        <v>676198.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>674048.2</v>
+        <v>676198.2</v>
       </c>
     </row>
     <row r="4">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>674048.2</v>
+        <v>676198.2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>674048.2</v>
+        <v>676198.2</v>
       </c>
     </row>
     <row r="5">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>674048.2</v>
+        <v>676198.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>674048.2</v>
+        <v>676198.2</v>
       </c>
     </row>
     <row r="6">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>674048.2</v>
+        <v>676198.2</v>
       </c>
       <c r="E6" t="n">
         <v>400000</v>
       </c>
       <c r="F6" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
     </row>
     <row r="7">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
     </row>
     <row r="8">
@@ -945,13 +945,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
     </row>
     <row r="9">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
     </row>
     <row r="10">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
     </row>
     <row r="11">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1074048.2</v>
+        <v>1076198.2</v>
       </c>
       <c r="E11" t="n">
         <v>180000</v>
       </c>
       <c r="F11" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
     </row>
     <row r="12">
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
     </row>
     <row r="13">
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
     </row>
     <row r="14">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
     </row>
     <row r="15">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
     </row>
     <row r="16">
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
     </row>
     <row r="17">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
     </row>
     <row r="18">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
     </row>
     <row r="19">
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1254048.2</v>
+        <v>1256198.2</v>
       </c>
       <c r="E19" t="n">
         <v>-400000</v>
       </c>
       <c r="F19" t="n">
-        <v>854048.2</v>
+        <v>856198.2</v>
       </c>
     </row>
     <row r="20">
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>854048.2</v>
+        <v>856198.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>854048.2</v>
+        <v>856198.2</v>
       </c>
     </row>
     <row r="21">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>854048.2</v>
+        <v>856198.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>854048.2</v>
+        <v>856198.2</v>
       </c>
     </row>
     <row r="22">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>854048.2</v>
+        <v>856198.2</v>
       </c>
       <c r="E22" t="n">
         <v>-115280.1</v>
       </c>
       <c r="F22" t="n">
-        <v>738768.1</v>
+        <v>740918.1</v>
       </c>
     </row>
     <row r="23">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>738768.1</v>
+        <v>740918.1</v>
       </c>
       <c r="E23" t="n">
         <v>225.09</v>
       </c>
       <c r="F23" t="n">
-        <v>738993.1899999999</v>
+        <v>741143.1899999999</v>
       </c>
     </row>
   </sheetData>
